--- a/Output/individual_characteristics_missing_diagnostics.xlsx
+++ b/Output/individual_characteristics_missing_diagnostics.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rural</t>
   </si>
 </sst>
 </file>
@@ -615,23 +612,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7620</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7620</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
